--- a/public/dashboard.xlsx
+++ b/public/dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qlstm\OneDrive\바탕 화면\졸업생 데이터\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qlstm\OneDrive\바탕 화면\업무\05. 홈페이지 구축\02. 대생인재뱅크 시스템\daesaeng-injaero-fixed-20260331\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E730D69D-D9C8-4F03-938F-4B1AB1D0DFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5790476E-F844-4A13-B897-716B2ABA5C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="학생통합DB" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">학생통합DB!$A$1:$X$947</definedName>
   </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6225" uniqueCount="2441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6235" uniqueCount="2449">
   <si>
     <t>학생ID</t>
   </si>
@@ -7395,6 +7395,34 @@
   <si>
     <t>중도탈락</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008.01.23.</t>
+  </si>
+  <si>
+    <t>대전대성중학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007.06.14.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복학생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008.05.06.</t>
+  </si>
+  <si>
+    <t>01057974427</t>
+  </si>
+  <si>
+    <t>01095764456</t>
   </si>
 </sst>
 </file>
@@ -7436,7 +7464,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7467,6 +7495,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -7495,7 +7529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7533,6 +7567,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10289,7 +10326,7 @@
         <v>171</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>30</v>
@@ -10353,7 +10390,7 @@
         <v>170.6</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>30</v>
@@ -10417,7 +10454,7 @@
         <v>227.4</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>30</v>
@@ -10481,7 +10518,7 @@
         <v>166.95</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>30</v>
@@ -10537,7 +10574,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="9"/>
       <c r="I43" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>30</v>
@@ -10593,7 +10630,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="9"/>
       <c r="I44" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>30</v>
@@ -10657,7 +10694,7 @@
         <v>163.5</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>30</v>
@@ -10721,7 +10758,7 @@
         <v>169.8</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>30</v>
@@ -10785,7 +10822,7 @@
         <v>207.6</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>30</v>
@@ -10849,7 +10886,7 @@
         <v>172.5</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>30</v>
@@ -10913,7 +10950,7 @@
         <v>163.30000000000001</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>30</v>
@@ -10977,7 +11014,7 @@
         <v>177.55</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>30</v>
@@ -11041,7 +11078,7 @@
         <v>156.30000000000001</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>30</v>
@@ -11105,7 +11142,7 @@
         <v>192.5</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>30</v>
@@ -31073,18 +31110,20 @@
       <c r="C341" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D341" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E341" s="4"/>
+      <c r="D341" s="4" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>2447</v>
+      </c>
       <c r="F341" s="5">
         <v>2024</v>
       </c>
-      <c r="G341" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H341" s="9" t="e">
-        <v>#N/A</v>
+      <c r="G341" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H341" s="9">
+        <v>160.6</v>
       </c>
       <c r="I341" s="4" t="s">
         <v>103</v>
@@ -32143,18 +32182,18 @@
       <c r="C357" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D357" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D357" s="4" t="s">
+        <v>2444</v>
       </c>
       <c r="E357" s="4"/>
       <c r="F357" s="5">
         <v>2024</v>
       </c>
-      <c r="G357" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H357" s="9" t="e">
-        <v>#N/A</v>
+      <c r="G357" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="H357" s="14" t="s">
+        <v>2445</v>
       </c>
       <c r="I357" s="4" t="s">
         <v>163</v>
@@ -32814,7 +32853,9 @@
       <c r="D367" s="4" t="s">
         <v>1121</v>
       </c>
-      <c r="E367" s="4"/>
+      <c r="E367" s="4" t="s">
+        <v>2448</v>
+      </c>
       <c r="F367" s="5">
         <v>2024</v>
       </c>
@@ -32822,7 +32863,7 @@
         <v>246</v>
       </c>
       <c r="H367" s="9">
-        <v>270.2</v>
+        <v>145.6</v>
       </c>
       <c r="I367" s="4" t="s">
         <v>163</v>
@@ -37566,18 +37607,18 @@
       <c r="C438" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D438" s="4" t="e">
-        <v>#N/A</v>
+      <c r="D438" s="4" t="s">
+        <v>2441</v>
       </c>
       <c r="E438" s="4"/>
       <c r="F438" s="5">
         <v>2024</v>
       </c>
-      <c r="G438" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H438" s="9" t="e">
-        <v>#N/A</v>
+      <c r="G438" s="4" t="s">
+        <v>2442</v>
+      </c>
+      <c r="H438" s="14" t="s">
+        <v>2443</v>
       </c>
       <c r="I438" s="4" t="s">
         <v>442</v>
